--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N53_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N53_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.53519014539115</v>
+        <v>1.224468398626062</v>
       </c>
       <c r="D2" t="n">
-        <v>5.82088078053695</v>
+        <v>0.9458931268372545</v>
       </c>
       <c r="E2" t="n">
-        <v>19.73279033162812</v>
+        <v>3.206578428889569</v>
       </c>
       <c r="F2" t="n">
-        <v>20.62065113620795</v>
+        <v>3.350855809633793</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.55688487079793</v>
+        <v>4.802993791504663</v>
       </c>
       <c r="D3" t="n">
-        <v>29.95798824890801</v>
+        <v>4.868173090447551</v>
       </c>
       <c r="E3" t="n">
-        <v>19.73279033162812</v>
+        <v>3.206578428889569</v>
       </c>
       <c r="F3" t="n">
-        <v>20.62065113620795</v>
+        <v>3.350855809633793</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.2833497354385</v>
+        <v>9.633544332008757</v>
       </c>
       <c r="D4" t="n">
-        <v>60.09571363323145</v>
+        <v>9.765553465400112</v>
       </c>
       <c r="E4" t="n">
-        <v>19.73279033162812</v>
+        <v>3.206578428889569</v>
       </c>
       <c r="F4" t="n">
-        <v>20.62065113620795</v>
+        <v>3.350855809633793</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>15.44372946167332</v>
+        <v>2.509606037521914</v>
       </c>
       <c r="D5" t="n">
-        <v>14.75489854301799</v>
+        <v>2.397671013240423</v>
       </c>
       <c r="E5" t="n">
-        <v>19.73279033162812</v>
+        <v>3.206578428889569</v>
       </c>
       <c r="F5" t="n">
-        <v>20.62065113620795</v>
+        <v>3.350855809633793</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
